--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N72_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N72_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.05553760761754</v>
+        <v>6.346524861237851</v>
       </c>
       <c r="D2" t="n">
-        <v>40.38852428176039</v>
+        <v>6.563135195786064</v>
       </c>
       <c r="E2" t="n">
-        <v>8.30336341841247</v>
+        <v>1.349296555492027</v>
       </c>
       <c r="F2" t="n">
-        <v>11.80259725537219</v>
+        <v>1.917922053997982</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.59853537719471</v>
+        <v>5.45976199879414</v>
       </c>
       <c r="D3" t="n">
-        <v>53.11735591740804</v>
+        <v>8.631570336578807</v>
       </c>
       <c r="E3" t="n">
-        <v>8.30336341841247</v>
+        <v>1.349296555492027</v>
       </c>
       <c r="F3" t="n">
-        <v>11.80259725537219</v>
+        <v>1.917922053997982</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.23305847418983</v>
+        <v>3.125372002055847</v>
       </c>
       <c r="D4" t="n">
-        <v>19.54109754080427</v>
+        <v>3.175428350380694</v>
       </c>
       <c r="E4" t="n">
-        <v>8.30336341841247</v>
+        <v>1.349296555492027</v>
       </c>
       <c r="F4" t="n">
-        <v>11.80259725537219</v>
+        <v>1.917922053997982</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.54490378128249</v>
+        <v>5.288546864458404</v>
       </c>
       <c r="D5" t="n">
-        <v>33.60057031692047</v>
+        <v>5.460092676499576</v>
       </c>
       <c r="E5" t="n">
-        <v>8.30336341841247</v>
+        <v>1.349296555492027</v>
       </c>
       <c r="F5" t="n">
-        <v>11.80259725537219</v>
+        <v>1.917922053997982</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.73643532991624</v>
+        <v>4.994670741111389</v>
       </c>
       <c r="D6" t="n">
-        <v>31.36182640399485</v>
+        <v>5.096296790649163</v>
       </c>
       <c r="E6" t="n">
-        <v>8.30336341841247</v>
+        <v>1.349296555492027</v>
       </c>
       <c r="F6" t="n">
-        <v>11.80259725537219</v>
+        <v>1.917922053997982</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.5689274239512</v>
+        <v>7.56745070639207</v>
       </c>
       <c r="D7" t="n">
-        <v>52.07628863940304</v>
+        <v>8.462396903902993</v>
       </c>
       <c r="E7" t="n">
-        <v>8.30336341841247</v>
+        <v>1.349296555492027</v>
       </c>
       <c r="F7" t="n">
-        <v>11.80259725537219</v>
+        <v>1.917922053997982</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
